--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487580_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487580_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0783</v>
+        <v>4.4447</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3581</v>
+        <v>4.0788</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7202</v>
+        <v>0.3659</v>
       </c>
       <c r="G2" t="n">
         <v>0.7689</v>
@@ -610,13 +610,13 @@
         <v>3.6866</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9228</v>
+        <v>1.2892</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3492</v>
+        <v>1.0699</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5736</v>
+        <v>0.2193</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3299</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4177</v>
+        <v>2.7742</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6221</v>
+        <v>1.8424</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7956</v>
+        <v>0.9319</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3221</v>
@@ -688,13 +688,13 @@
         <v>3.2985</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6935</v>
+        <v>1.0501</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1377</v>
+        <v>1.3579</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4441</v>
+        <v>-0.3078</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2821</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4487</v>
+        <v>2.476</v>
       </c>
       <c r="E4" t="n">
         <v>1.7269</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7218</v>
+        <v>0.7491</v>
       </c>
       <c r="G4" t="n">
         <v>1.9696</v>
@@ -766,13 +766,13 @@
         <v>0.7761</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.297</v>
+        <v>-0.2697</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>Y. RODRÍGUEZ MACHÍN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2326</v>
+        <v>0.3145</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7511</v>
+        <v>-1.0395</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.5185</v>
+        <v>1.354</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.2809</v>
+        <v>0.6016</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7761</v>
+        <v>-1.1213</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5048</v>
+        <v>1.7228</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0369</v>
+        <v>0.2298</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9557</v>
+        <v>-1.2317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08119999999999999</v>
+        <v>1.4615</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.3178</v>
+        <v>0.3718</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7318</v>
+        <v>0.1104</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.586</v>
+        <v>0.2614</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>1.1642</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>2.1344</v>
       </c>
       <c r="S5" t="n">
-        <v>3.5313</v>
+        <v>-0.2274</v>
       </c>
       <c r="T5" t="n">
-        <v>3.8963</v>
+        <v>-0.2992</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3649</v>
+        <v>0.0718</v>
       </c>
       <c r="V5" t="n">
-        <v>1.788</v>
+        <v>-1.2239</v>
       </c>
       <c r="W5" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. RODRÍGUEZ MACHÍN</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7723</v>
+        <v>0.1365</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7998</v>
+        <v>3.7095</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5721</v>
+        <v>-3.573</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6016</v>
+        <v>-3.2809</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1213</v>
+        <v>-0.7761</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7228</v>
+        <v>-2.5048</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2298</v>
+        <v>1.0369</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2317</v>
+        <v>0.9557</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4615</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3718</v>
+        <v>-4.3178</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1104</v>
+        <v>-1.7318</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2614</v>
+        <v>-2.586</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1344</v>
+        <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2304</v>
+        <v>1.4353</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0595</v>
+        <v>1.8548</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2898</v>
+        <v>-0.4194</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2239</v>
+        <v>1.788</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0997</v>
+        <v>0.127</v>
       </c>
       <c r="E7" t="n">
         <v>-0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1397</v>
+        <v>0.167</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0519</v>
@@ -1000,13 +1000,13 @@
         <v>0.194</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0424</v>
+        <v>-0.0151</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9737</v>
+        <v>-0.4606</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.657</v>
+        <v>-1.3347</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6833</v>
+        <v>0.8741</v>
       </c>
       <c r="G8" t="n">
         <v>-4.5737</v>
@@ -1078,13 +1078,13 @@
         <v>3.2985</v>
       </c>
       <c r="S8" t="n">
-        <v>-1</v>
+        <v>0.5131</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.7301</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4078</v>
+        <v>-0.217</v>
       </c>
       <c r="V8" t="n">
         <v>1.2716</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4187</v>
+        <v>-1.9483</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4089</v>
+        <v>-0.7478</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0098</v>
+        <v>-1.2005</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7453</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.3791</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6057</v>
+        <v>0.0555</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5144</v>
+        <v>0.3236</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5469</v>
+        <v>-2.5488</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2496</v>
+        <v>-0.6875</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2974</v>
+        <v>-1.8613</v>
       </c>
       <c r="G10" t="n">
         <v>-4.8104</v>
@@ -1234,13 +1234,13 @@
         <v>3.8806</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.6187</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5018</v>
+        <v>0.0602</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1168</v>
+        <v>-0.6808</v>
       </c>
       <c r="V10" t="n">
         <v>0.9418</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.1474</v>
+        <v>-6.747</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0304</v>
+        <v>-2.63</v>
       </c>
       <c r="F11" t="n">
         <v>-4.117</v>
@@ -1312,10 +1312,10 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0184</v>
+        <v>-0.618</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4845</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="U11" t="n">
         <v>-0.5339</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.037400000000002</v>
+        <v>-1.431800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.272499999999998</v>
+        <v>4.878100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.31</v>
+        <v>-6.3098</v>
       </c>
       <c r="G12" t="n">
         <v>-14.709</v>
       </c>
       <c r="H12" t="n">
-        <v>-8.007999999999999</v>
+        <v>-8.008000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.701199999999999</v>
+        <v>-6.7012</v>
       </c>
       <c r="J12" t="n">
         <v>4.4113</v>
@@ -1369,7 +1369,7 @@
         <v>1.4913</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9202</v>
+        <v>2.920199999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-19.1205</v>
@@ -1378,10 +1378,10 @@
         <v>-9.4993</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.620999999999999</v>
+        <v>-9.621</v>
       </c>
       <c r="P12" t="n">
-        <v>9.701500000000001</v>
+        <v>9.701499999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-10.6719</v>
@@ -1390,10 +1390,10 @@
         <v>20.3732</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3102</v>
+        <v>2.916100000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>3.897199999999999</v>
+        <v>4.5028</v>
       </c>
       <c r="U12" t="n">
         <v>-1.5868</v>
@@ -1405,7 +1405,7 @@
         <v>6.6357</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.976100000000001</v>
+        <v>-5.9761</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8402</v>
+        <v>4.8632</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9399</v>
+        <v>5.6386</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0997</v>
+        <v>-0.7754</v>
       </c>
       <c r="G13" t="n">
         <v>4.9155</v>
@@ -1468,13 +1468,13 @@
         <v>0.9702</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1949</v>
+        <v>0.2179</v>
       </c>
       <c r="T13" t="n">
-        <v>2.27</v>
+        <v>0.9687</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0751</v>
+        <v>-0.7509</v>
       </c>
       <c r="V13" t="n">
         <v>0.894</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5624</v>
+        <v>4.108</v>
       </c>
       <c r="E14" t="n">
-        <v>3.423</v>
+        <v>3.7233</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1394</v>
+        <v>0.3847</v>
       </c>
       <c r="G14" t="n">
         <v>5.1575</v>
@@ -1546,13 +1546,13 @@
         <v>1.1642</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.819</v>
+        <v>-0.2734</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4116</v>
+        <v>-0.1113</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4073</v>
+        <v>-0.162</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9163</v>
+        <v>0.8528</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1386</v>
+        <v>0.2387</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7776999999999999</v>
+        <v>0.6142</v>
       </c>
       <c r="G15" t="n">
         <v>0.4328</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0357</v>
+        <v>-0.0278</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.157</v>
+        <v>-0.0569</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1927</v>
+        <v>0.0292</v>
       </c>
       <c r="V15" t="n">
         <v>1.2239</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0609</v>
+        <v>0.334</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9737</v>
+        <v>1.274</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4651</v>
@@ -1702,13 +1702,13 @@
         <v>0.5821</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3098</v>
+        <v>-0.0367</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3511</v>
+        <v>-0.0508</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0413</v>
+        <v>0.014</v>
       </c>
       <c r="V16" t="n">
         <v>1.2239</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0139</v>
+        <v>0.3142</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6787</v>
+        <v>-0.3784</v>
       </c>
       <c r="F17" t="n">
         <v>0.6926</v>
@@ -1780,10 +1780,10 @@
         <v>0.194</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1099</v>
+        <v>0.1904</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2423</v>
+        <v>0.058</v>
       </c>
       <c r="U17" t="n">
         <v>0.1324</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5522</v>
+        <v>-0.1635</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1468</v>
+        <v>0.6472</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6989</v>
+        <v>-0.8108</v>
       </c>
       <c r="G18" t="n">
         <v>2.3527</v>
@@ -1858,13 +1858,13 @@
         <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0989</v>
+        <v>-0.7102000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5081</v>
+        <v>-0.0076</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5908</v>
+        <v>-0.7026</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2239</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0076</v>
+        <v>-1.0185</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8471</v>
+        <v>-0.7367</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1605</v>
+        <v>-0.2818</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.04</v>
+        <v>0.3391</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6255</v>
+        <v>1.1221</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6655</v>
+        <v>-0.783</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.1295</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5613</v>
+        <v>1.3017</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6979</v>
+        <v>-1.1723</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9034</v>
+        <v>0.2096</v>
       </c>
       <c r="N19" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.1796</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9677</v>
+        <v>0.3893</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5265</v>
+        <v>-1.1039</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7537</v>
+        <v>-0.1781</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2272</v>
+        <v>-0.9258</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3299</v>
+        <v>-1.2239</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3299</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4974</v>
+        <v>-1.6288</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8368</v>
+        <v>-1.2475</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6606</v>
+        <v>-0.3813</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3391</v>
+        <v>-0.04</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1221</v>
+        <v>1.6255</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.783</v>
+        <v>-1.6655</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1295</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3017</v>
+        <v>1.5613</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1723</v>
+        <v>-0.6979</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2096</v>
+        <v>-0.9034</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1796</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3893</v>
+        <v>-0.9677</v>
       </c>
       <c r="P20" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-2.1344</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.9702</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.9702</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.9403</v>
-      </c>
       <c r="S20" t="n">
-        <v>-1.5828</v>
+        <v>-0.0948</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2782</v>
+        <v>0.3533</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3046</v>
+        <v>-0.448</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2239</v>
+        <v>-0.3299</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2821</v>
+        <v>-0.3299</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.445</v>
+        <v>-2.1565</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5933</v>
+        <v>0.9937</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0384</v>
+        <v>-3.1502</v>
       </c>
       <c r="G21" t="n">
         <v>2.2176</v>
@@ -2092,13 +2092,13 @@
         <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2745</v>
+        <v>0.014</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.157</v>
+        <v>0.2434</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1175</v>
+        <v>-0.2293</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4477</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.854</v>
+        <v>-2.8</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5426</v>
+        <v>-3.8429</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6886</v>
+        <v>1.0429</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1008</v>
@@ -2170,13 +2170,13 @@
         <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1274</v>
+        <v>0.1814</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6684</v>
+        <v>0.3681</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.541</v>
+        <v>-0.1867</v>
       </c>
       <c r="V22" t="n">
         <v>1.2239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.037499999999999</v>
+        <v>2.704899999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>6.310099999999998</v>
+        <v>6.31</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.2726</v>
+        <v>-3.6051</v>
       </c>
       <c r="G23" t="n">
         <v>14.7092</v>
@@ -2248,13 +2248,13 @@
         <v>10.6719</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.3104</v>
+        <v>-1.6431</v>
       </c>
       <c r="T23" t="n">
         <v>1.5868</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.8971</v>
+        <v>-3.2297</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6597000000000004</v>
